--- a/data/trans_orig/P1425-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2007</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464938</t>
+          <t>466169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472840</t>
+          <t>472860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298804</t>
+          <t>298422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305754</t>
+          <t>305745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>767301</t>
+          <t>769405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>778369</t>
+          <t>778353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353988</t>
+          <t>354271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365071</t>
+          <t>365033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361377</t>
+          <t>361996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370884</t>
+          <t>370661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720719</t>
+          <t>720947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734140</t>
+          <t>733815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531798</t>
+          <t>532088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540544</t>
+          <t>540592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160106</t>
+          <t>160175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>696558</t>
+          <t>695297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707281</t>
+          <t>707321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1215175</t>
+          <t>1215613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1229880</t>
+          <t>1230347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>699065</t>
+          <t>698326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710274</t>
+          <t>709631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1918145</t>
+          <t>1920514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937839</t>
+          <t>1937770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,82 +2119,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7890</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16438</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>16021</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>9359</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>25623</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15726</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>16021</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>8864</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>26493</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335463</t>
+          <t>334962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346990</t>
+          <t>346844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,82 +2232,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>560862</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>552314</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>565497</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>903286</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>893684</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>909948</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>98,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>560862</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>553026</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>565480</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>903286</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>892814</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>910443</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26018</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287560</t>
+          <t>286928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296309</t>
+          <t>296282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1228975</t>
+          <t>1228766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1243075</t>
+          <t>1243432</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1520942</t>
+          <t>1519362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1537334</t>
+          <t>1537137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54483</t>
+          <t>55395</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,82 +2805,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>36848</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>25792</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>49752</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>77580</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>61616</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>97317</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>36848</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>26087</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>49893</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>77580</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>60484</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>98551</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3215707</t>
+          <t>3214795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3239765</t>
+          <t>3240397</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,82 +2918,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3341276</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3328372</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3352332</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6426</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6570734</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6550997</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6586698</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>99,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3341276</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3328231</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3352037</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6426</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6570734</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6549763</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6587830</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2012</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432011</t>
+          <t>432184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309148</t>
+          <t>308139</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>745606</t>
+          <t>744807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401120</t>
+          <t>401872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417679</t>
+          <t>417669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329142</t>
+          <t>327920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739278</t>
+          <t>737990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754552</t>
+          <t>754585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621451</t>
+          <t>621476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628478</t>
+          <t>628495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>253583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>878264</t>
+          <t>878120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887577</t>
+          <t>887589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9371</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1140348</t>
+          <t>1140888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1154850</t>
+          <t>1154910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>755351</t>
+          <t>755717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763765</t>
+          <t>763769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1900060</t>
+          <t>1901083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917367</t>
+          <t>1917621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>20653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>495020</t>
+          <t>495637</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506606</t>
+          <t>507349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>749965</t>
+          <t>749663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759158</t>
+          <t>759186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1248911</t>
+          <t>1250190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1264425</t>
+          <t>1264321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,47 +5097,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9141</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4259</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>17988</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>9141</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>17562</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258233</t>
+          <t>258057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265866</t>
+          <t>265925</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,49 +5210,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1100210</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1091363</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1105092</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1100210</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1091789</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1105100</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1297</t>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1354062</t>
+          <t>1354632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1369942</t>
+          <t>1370020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19449</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44883</t>
+          <t>44592</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>32608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70351</t>
+          <t>69241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3377027</t>
+          <t>3377318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3402461</t>
+          <t>3401574</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3513643</t>
+          <t>3514307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3533920</t>
+          <t>3533013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6898474</t>
+          <t>6899584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6929693</t>
+          <t>6930453</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2016</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420965</t>
+          <t>421100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428127</t>
+          <t>428132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339843</t>
+          <t>340952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765175</t>
+          <t>764085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774186</t>
+          <t>774171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370513</t>
+          <t>369570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367069</t>
+          <t>367042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740817</t>
+          <t>741376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748540</t>
+          <t>748544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508372</t>
+          <t>509586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519898</t>
+          <t>519925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675022</t>
+          <t>675548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686026</t>
+          <t>686041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133508</t>
+          <t>1134027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145412</t>
+          <t>1145827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>810545</t>
+          <t>811602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>824605</t>
+          <t>824606</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950928</t>
+          <t>1951544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967939</t>
+          <t>1967772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606906</t>
+          <t>606891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>618564</t>
+          <t>618350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>718537</t>
+          <t>719402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734217</t>
+          <t>734432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332853</t>
+          <t>1334085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1350889</t>
+          <t>1350851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>24714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>32944</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274838</t>
+          <t>274966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285001</t>
+          <t>284946</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1056192</t>
+          <t>1057311</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1072881</t>
+          <t>1073387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1336526</t>
+          <t>1336226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1354586</t>
+          <t>1354975</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43319</t>
+          <t>45308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47058</t>
+          <t>48835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85061</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3342403</t>
+          <t>3340414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3364681</t>
+          <t>3363365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3484538</t>
+          <t>3482761</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3508823</t>
+          <t>3508589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6832257</t>
+          <t>6831877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6866728</t>
+          <t>6868378</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1425-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466169</t>
+          <t>465506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472860</t>
+          <t>472840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298422</t>
+          <t>298168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305745</t>
+          <t>305751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>769405</t>
+          <t>768111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>778353</t>
+          <t>778356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354271</t>
+          <t>353712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365033</t>
+          <t>365062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361996</t>
+          <t>362482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370661</t>
+          <t>370777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720947</t>
+          <t>721372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733815</t>
+          <t>734191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532088</t>
+          <t>530985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540592</t>
+          <t>540542</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160175</t>
+          <t>161018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>695297</t>
+          <t>696982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707321</t>
+          <t>707367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1215613</t>
+          <t>1215143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1230347</t>
+          <t>1229651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>698326</t>
+          <t>699160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>709631</t>
+          <t>710311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920514</t>
+          <t>1917955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937770</t>
+          <t>1937384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>334962</t>
+          <t>334379</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346844</t>
+          <t>346697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>552314</t>
+          <t>554374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>565497</t>
+          <t>565708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>893684</t>
+          <t>892413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>909948</t>
+          <t>910439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27598</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286928</t>
+          <t>286004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296282</t>
+          <t>296293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1228766</t>
+          <t>1229306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1243432</t>
+          <t>1243241</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1519362</t>
+          <t>1521950</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1537137</t>
+          <t>1537017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29793</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55395</t>
+          <t>54248</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>24989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49752</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61616</t>
+          <t>60461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97317</t>
+          <t>95794</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3214795</t>
+          <t>3215942</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3240397</t>
+          <t>3240437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3328372</t>
+          <t>3328141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3352332</t>
+          <t>3353135</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6550997</t>
+          <t>6552520</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6586698</t>
+          <t>6587853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432184</t>
+          <t>432587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308139</t>
+          <t>309899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>744807</t>
+          <t>744069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401872</t>
+          <t>403184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417669</t>
+          <t>417667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327920</t>
+          <t>328959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>737990</t>
+          <t>738374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754585</t>
+          <t>755052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621476</t>
+          <t>621528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628495</t>
+          <t>628485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253583</t>
+          <t>253646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>878120</t>
+          <t>877451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887589</t>
+          <t>887556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>18578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22648</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1140888</t>
+          <t>1140431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1154910</t>
+          <t>1155004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>755717</t>
+          <t>756208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763769</t>
+          <t>763780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901083</t>
+          <t>1902453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917621</t>
+          <t>1916799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>21891</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>495637</t>
+          <t>495003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507349</t>
+          <t>506495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>749663</t>
+          <t>750481</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759186</t>
+          <t>759155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1250190</t>
+          <t>1248952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1264321</t>
+          <t>1263546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>22379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258057</t>
+          <t>257901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265925</t>
+          <t>265921</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1091363</t>
+          <t>1090965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1105092</t>
+          <t>1105116</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1354632</t>
+          <t>1353854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1370020</t>
+          <t>1368984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>34347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69241</t>
+          <t>71293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3377318</t>
+          <t>3377707</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3401574</t>
+          <t>3401798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3514307</t>
+          <t>3512568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3533013</t>
+          <t>3533802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6899584</t>
+          <t>6897532</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6930453</t>
+          <t>6930443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421100</t>
+          <t>421054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428132</t>
+          <t>428124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340952</t>
+          <t>340140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>764085</t>
+          <t>764663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>774171</t>
+          <t>774162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369570</t>
+          <t>370533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367042</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741376</t>
+          <t>741301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748544</t>
+          <t>748547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509586</t>
+          <t>508197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519925</t>
+          <t>519862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675548</t>
+          <t>673358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686041</t>
+          <t>685885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1134027</t>
+          <t>1134170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1145827</t>
+          <t>1145334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>811602</t>
+          <t>811038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>824606</t>
+          <t>823795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951544</t>
+          <t>1952011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967772</t>
+          <t>1968388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24865</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606891</t>
+          <t>606085</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>618350</t>
+          <t>618244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719402</t>
+          <t>719387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734432</t>
+          <t>734431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1334085</t>
+          <t>1333338</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1350851</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24714</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>33919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274966</t>
+          <t>274904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284946</t>
+          <t>284301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1057311</t>
+          <t>1055809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1073387</t>
+          <t>1072824</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1336226</t>
+          <t>1335251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1354975</t>
+          <t>1355105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45308</t>
+          <t>44237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23007</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>48079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t>82877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3340414</t>
+          <t>3341485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3363365</t>
+          <t>3364197</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3482761</t>
+          <t>3483517</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3508589</t>
+          <t>3508933</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6831877</t>
+          <t>6834441</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6868378</t>
+          <t>6868424</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
